--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87403</v>
+        <v>87406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87579</v>
+        <v>87582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87472</v>
+        <v>87475</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87406</v>
+        <v>87416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91554</v>
+        <v>91564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91554</v>
+        <v>91564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137254354</v>
       </c>
       <c r="B6" t="n">
-        <v>57934</v>
+        <v>57944</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87582</v>
+        <v>87592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87475</v>
+        <v>87485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87416</v>
+        <v>87417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91564</v>
+        <v>91565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87592</v>
+        <v>87593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87485</v>
+        <v>87486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87417</v>
+        <v>87420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91565</v>
+        <v>91568</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137254354</v>
       </c>
       <c r="B6" t="n">
-        <v>57944</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87593</v>
+        <v>87596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87486</v>
+        <v>87489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91568</v>
+        <v>91570</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91568</v>
+        <v>91570</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87420</v>
+        <v>87425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91570</v>
+        <v>91575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91570</v>
+        <v>91575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137254354</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87596</v>
+        <v>87601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87489</v>
+        <v>87494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87425</v>
+        <v>87436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91575</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91575</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87601</v>
+        <v>87612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87494</v>
+        <v>87505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87436</v>
+        <v>87437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87612</v>
+        <v>87613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87505</v>
+        <v>87506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87437</v>
+        <v>87440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>91591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91588</v>
+        <v>91591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87506</v>
+        <v>87509</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 39400-2026 artfynd.xlsx
+++ b/artfynd/A 39400-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137251695</v>
       </c>
       <c r="B2" t="n">
-        <v>87440</v>
+        <v>87444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137251693</v>
       </c>
       <c r="B3" t="n">
-        <v>91591</v>
+        <v>91595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137252400</v>
       </c>
       <c r="B4" t="n">
-        <v>91591</v>
+        <v>91595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137252397</v>
       </c>
       <c r="B5" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137254354</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57949</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>137251694</v>
       </c>
       <c r="B7" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>137252396</v>
       </c>
       <c r="B8" t="n">
-        <v>87616</v>
+        <v>87620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>137252399</v>
       </c>
       <c r="B9" t="n">
-        <v>87509</v>
+        <v>87513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
